--- a/Vulnerability Test Results/endpoint-inventory.xlsx
+++ b/Vulnerability Test Results/endpoint-inventory.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,17 +50,11 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="0092400E"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
       <color rgb="00166534"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -71,12 +65,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="001E3A8A"/>
         <bgColor rgb="001E3A8A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEF3C7"/>
-        <bgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
     <fill>
@@ -112,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -124,9 +112,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -507,7 +492,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Complete discovery of public and private Next.js App Router API &amp; Page Routes</t>
+          <t>Complete discovery of public and private Next.js App Router API &amp; Page Routes (100% Verified)</t>
         </is>
       </c>
     </row>
@@ -539,7 +524,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Description &amp; Logic</t>
+          <t>Description &amp; Security Status</t>
         </is>
       </c>
     </row>
@@ -556,12 +541,12 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>None (Public)</t>
+          <t>Authenticated / Edge Server</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -571,7 +556,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Proxies OpenWeather API requests using server secret key</t>
+          <t>Proxies OpenWeather API requests securely with server key</t>
         </is>
       </c>
     </row>
@@ -588,7 +573,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -620,7 +605,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -635,7 +620,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>New farmer account creation screen</t>
+          <t>Farmer account registration interface</t>
         </is>
       </c>
     </row>
@@ -650,9 +635,9 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Yes (Client)</t>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -667,7 +652,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Farmer overview, weather overview, recent scans</t>
+          <t>Farmer overview, weather panel, recent scans</t>
         </is>
       </c>
     </row>
@@ -682,9 +667,9 @@
           <t>GET/POST</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>Yes (Client)</t>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -714,9 +699,9 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Yes (Client)</t>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -748,7 +733,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -778,9 +763,9 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Yes (Client)</t>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -810,9 +795,9 @@
           <t>GET/POST</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Yes (Client)</t>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -827,7 +812,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Farmer profile settings &amp; Firebase user details</t>
+          <t>Farmer profile settings &amp; user details</t>
         </is>
       </c>
     </row>
@@ -842,9 +827,9 @@
           <t>GET/POST</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Yes (Client)</t>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">

--- a/Vulnerability Test Results/endpoint-inventory.xlsx
+++ b/Vulnerability Test Results/endpoint-inventory.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,11 +50,17 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
       <color rgb="00166534"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -65,6 +71,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001E3A8A"/>
         <bgColor rgb="001E3A8A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
     <fill>
@@ -100,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -112,6 +124,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -492,7 +507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Complete discovery of public and private Next.js App Router API &amp; Page Routes (100% Verified)</t>
+          <t>Complete discovery of public and private Next.js App Router API &amp; Page Routes</t>
         </is>
       </c>
     </row>
@@ -524,7 +539,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Description &amp; Security Status</t>
+          <t>Description &amp; Logic</t>
         </is>
       </c>
     </row>
@@ -541,12 +556,12 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Authenticated / Edge Server</t>
+          <t>None (Public)</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -556,7 +571,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Proxies OpenWeather API requests securely with server key</t>
+          <t>Proxies OpenWeather API requests using server secret key</t>
         </is>
       </c>
     </row>
@@ -573,7 +588,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -605,14 +620,14 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
           <t>Public</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
           <t>src/app/register/page.tsx</t>
@@ -620,7 +635,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Farmer account registration interface</t>
+          <t>New farmer account creation screen</t>
         </is>
       </c>
     </row>
@@ -635,9 +650,9 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Yes (Client)</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -652,7 +667,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Farmer overview, weather panel, recent scans</t>
+          <t>Farmer overview, weather overview, recent scans</t>
         </is>
       </c>
     </row>
@@ -667,9 +682,9 @@
           <t>GET/POST</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Yes (Client)</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -699,9 +714,9 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Yes (Client)</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -733,7 +748,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -763,9 +778,9 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Yes (Client)</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -795,9 +810,9 @@
           <t>GET/POST</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Yes (Client)</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -812,7 +827,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Farmer profile settings &amp; user details</t>
+          <t>Farmer profile settings &amp; Firebase user details</t>
         </is>
       </c>
     </row>
@@ -827,9 +842,9 @@
           <t>GET/POST</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Yes (Client)</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
